--- a/BWI/bestwine_output/bestwine_Tanzania.xlsx
+++ b/BWI/bestwine_output/bestwine_Tanzania.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA8"/>
+  <dimension ref="A1:AA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1348,6 +1348,208 @@
       <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Red'n White</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Red'n White</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>37802</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Dar Es Salaam</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Dar es Salam, Kinondoni</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Church Street, Plot 2074</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>http://rednwhite.info, http://www.rednwhite.com, https://rednwhite.co.tz</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>info@rednwhite.co.tz</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>+255 22 261 8202</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rednwhite/</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/red.white.9275</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/red.n.white/</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>Arjan Tiessen</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>General Manager / Executive Operations Manager</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/arjantiessen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Red'n White</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Red'n White</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>37802</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Dar Es Salaam</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Dar es Salam, Kinondoni</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Church Street, Plot 2074</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>http://rednwhite.info, http://www.rednwhite.com, https://rednwhite.co.tz</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>info@rednwhite.co.tz</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>+255 22 261 8202</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rednwhite/</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/red.white.9275</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/red.n.white/</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>Dieter Beyens</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dieter-beyens-11371910/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Tanzania.xlsx
+++ b/BWI/bestwine_output/bestwine_Tanzania.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1550,6 +1550,208 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Red'n White</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Red'n White</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>37802</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Dar Es Salaam</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Dar es Salam, Kinondoni</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Church Street, Plot 2074</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>http://rednwhite.info, http://www.rednwhite.com, https://rednwhite.co.tz</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>info@rednwhite.co.tz</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>+255 22 261 8202</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rednwhite/</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/red.white.9275</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/red.n.white/</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>Arjan Tiessen</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>General Manager / Executive Operations Manager</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/arjantiessen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Red'n White</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Red'n White</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>37802</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Dar Es Salaam</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Dar es Salam, Kinondoni</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Church Street, Plot 2074</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>http://rednwhite.info, http://www.rednwhite.com, https://rednwhite.co.tz</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>info@rednwhite.co.tz</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>+255 22 261 8202</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rednwhite/</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/red.white.9275</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/red.n.white/</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>Dieter Beyens</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dieter-beyens-11371910/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Tanzania.xlsx
+++ b/BWI/bestwine_output/bestwine_Tanzania.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA12"/>
+  <dimension ref="A1:AA14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1752,6 +1752,208 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Red'n White</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Red'n White</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>37802</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Dar Es Salaam</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Dar es Salam, Kinondoni</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Church Street, Plot 2074</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>http://rednwhite.info, http://www.rednwhite.com, https://rednwhite.co.tz</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>info@rednwhite.co.tz</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>+255 22 261 8202</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rednwhite/</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/red.white.9275</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/red.n.white/</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>Arjan Tiessen</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>General Manager / Executive Operations Manager</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/arjantiessen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Red'n White</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Red'n White</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>37802</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Dar Es Salaam</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Dar es Salam, Kinondoni</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Church Street, Plot 2074</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>http://rednwhite.info, http://www.rednwhite.com, https://rednwhite.co.tz</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>info@rednwhite.co.tz</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>+255 22 261 8202</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rednwhite/</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/red.white.9275</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/red.n.white/</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>Dieter Beyens</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dieter-beyens-11371910/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Tanzania.xlsx
+++ b/BWI/bestwine_output/bestwine_Tanzania.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA14"/>
+  <dimension ref="A1:AA16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1954,6 +1954,208 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Red'n White</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Red'n White</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>37802</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Dar Es Salaam</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Dar es Salam, Kinondoni</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Church Street, Plot 2074</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>http://rednwhite.info, http://www.rednwhite.com, https://rednwhite.co.tz</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>info@rednwhite.co.tz</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>+255 22 261 8202</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rednwhite/</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/red.white.9275</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/red.n.white/</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>Arjan Tiessen</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>General Manager / Executive Operations Manager</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/arjantiessen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Red'n White</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Red'n White</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>37802</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Dar Es Salaam</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Dar es Salam, Kinondoni</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Church Street, Plot 2074</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>http://rednwhite.info, http://www.rednwhite.com, https://rednwhite.co.tz</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>info@rednwhite.co.tz</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>+255 22 261 8202</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rednwhite/</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/red.white.9275</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/red.n.white/</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>Dieter Beyens</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dieter-beyens-11371910/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Tanzania.xlsx
+++ b/BWI/bestwine_output/bestwine_Tanzania.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA16"/>
+  <dimension ref="A1:AA18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2156,6 +2156,208 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Red'n White</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Red'n White</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>37802</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Dar Es Salaam</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Dar es Salam, Kinondoni</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Church Street, Plot 2074</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>http://rednwhite.info, http://www.rednwhite.com, https://rednwhite.co.tz</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>info@rednwhite.co.tz</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>+255 22 261 8202</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rednwhite/</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/red.white.9275</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/red.n.white/</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>Arjan Tiessen</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>General Manager / Executive Operations Manager</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/arjantiessen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Red'n White</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Red'n White</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>37802</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Dar Es Salaam</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Dar es Salam, Kinondoni</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Church Street, Plot 2074</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>http://rednwhite.info, http://www.rednwhite.com, https://rednwhite.co.tz</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>info@rednwhite.co.tz</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>+255 22 261 8202</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rednwhite/</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/red.white.9275</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/red.n.white/</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>Dieter Beyens</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dieter-beyens-11371910/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
